--- a/data_2_new.xlsx
+++ b/data_2_new.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="208">
   <si>
     <t xml:space="preserve">Без ПЧ</t>
   </si>
@@ -3417,6 +3417,9 @@
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
@@ -3451,6 +3454,9 @@
       <c r="J2" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K2" s="1" t="n">
+        <v>32</v>
+      </c>
       <c r="M2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3486,6 +3492,9 @@
       <c r="J3" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K3" s="1" t="n">
+        <v>32</v>
+      </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3521,6 +3530,9 @@
       <c r="J4" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K4" s="1" t="n">
+        <v>32</v>
+      </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3556,6 +3568,9 @@
       <c r="J5" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K5" s="1" t="n">
+        <v>32</v>
+      </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3591,6 +3606,9 @@
       <c r="J6" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K6" s="1" t="n">
+        <v>63</v>
+      </c>
       <c r="M6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3626,6 +3644,9 @@
       <c r="J7" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K7" s="1" t="n">
+        <v>63</v>
+      </c>
       <c r="M7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3661,6 +3682,9 @@
       <c r="J8" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K8" s="1" t="n">
+        <v>100</v>
+      </c>
       <c r="M8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3696,6 +3720,9 @@
       <c r="J9" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K9" s="1" t="n">
+        <v>100</v>
+      </c>
       <c r="M9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3731,6 +3758,9 @@
       <c r="J10" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K10" s="1" t="n">
+        <v>100</v>
+      </c>
       <c r="M10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3766,6 +3796,9 @@
       <c r="J11" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K11" s="1" t="n">
+        <v>100</v>
+      </c>
       <c r="M11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3800,6 +3833,9 @@
       <c r="J12" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K12" s="1" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
@@ -3833,6 +3869,9 @@
       <c r="J13" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K13" s="1" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
@@ -3866,6 +3905,9 @@
       <c r="J14" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K14" s="1" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
@@ -3899,6 +3941,9 @@
       <c r="J15" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K15" s="1" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
@@ -3932,6 +3977,9 @@
       <c r="J16" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K16" s="1" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
@@ -3965,6 +4013,9 @@
       <c r="J17" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K17" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
@@ -3998,6 +4049,9 @@
       <c r="J18" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K18" s="1" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
@@ -4031,6 +4085,9 @@
       <c r="J19" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K19" s="1" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
@@ -4064,6 +4121,9 @@
       <c r="J20" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K20" s="1" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
@@ -4097,6 +4157,9 @@
       <c r="J21" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K21" s="1" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
@@ -4130,6 +4193,9 @@
       <c r="J22" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K22" s="1" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
@@ -4163,6 +4229,9 @@
       <c r="J23" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K23" s="1" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
@@ -4196,6 +4265,9 @@
       <c r="J24" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K24" s="1" t="n">
+        <v>32</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
@@ -4229,6 +4301,9 @@
       <c r="J25" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K25" s="1" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
@@ -4262,6 +4337,9 @@
       <c r="J26" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K26" s="1" t="n">
+        <v>63</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
@@ -4295,6 +4373,9 @@
       <c r="J27" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K27" s="1" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
@@ -4328,6 +4409,9 @@
       <c r="J28" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K28" s="1" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
@@ -4361,6 +4445,9 @@
       <c r="J29" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K29" s="1" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
@@ -4394,6 +4481,9 @@
       <c r="J30" s="9" t="n">
         <v>46372</v>
       </c>
+      <c r="K30" s="1" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="13.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
@@ -4426,6 +4516,9 @@
       </c>
       <c r="J31" s="9" t="n">
         <v>46372</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <v>200</v>
       </c>
     </row>
   </sheetData>
